--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0053.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0053.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Rotating Mechanism</t>
+          <t>Cơ Chế Xoay</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sage</t>
+          <t>Hiền Nhân</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Máy thử nghiệm: Outdoor short</t>
+          <t>Máy Kiểm Tra: Ngoài trời (ngắn)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Phantom: Sentry Construct</t>
+          <t>Hồn Ma: Cấu Trúc Canh Gác</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Xian’ge_Ghế</t>
+          <t>Trưởng Lão Hiền</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Threnodian's Cocoon</t>
+          <t>Kén Threnodian</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Đến Honami City</t>
+          <t>Đến Thành phố Honami</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sound Capture Device</t>
+          <t>Thiết Bị Thu Âm</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Jinhsi Cube</t>
+          <t>Khối Kim Tư</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>- Móng Vuốt Hối Tiếc</t>
+          <t>Móng Vuốt Hối Tiếc</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Kiểm tra Sổ Khách</t>
+          <t>Xem Sổ Lưu Bút</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Vào Heart of the Crownless</t>
+          <t>Đến với Trái Tim Vô Vương</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Cô gái sôi nổi</t>
+          <t>Cô Gái Đầy Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đưa ra sự công nhận</t>
+          <t>Trao sự công nhận</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Moon-Chasing Festival</t>
+          <t>Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Học sinh Tò Mò</t>
+          <t>Học Sinh Tò Mò</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Gợi ý Mục tiêu Thử thách</t>
+          <t>Mục tiêu Thử Thách Gợi Ý</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Trưởng Lão Kỳ Cựu</t>
+          <t>Trưởng Lão Kì Cựu</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Jiangsheng</t>
+          <t>Khương Sinh</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Cô Gái Royan Chăm Chỉ</t>
+          <t>Cô gái Royan chăm học</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Busy Courier</t>
+          <t>Người đưa thư bận rộn</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Talkie</t>
+          <t>Bộ đàm</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Đến Shashou Cafe</t>
+          <t>Đến Quán cà phê Shashou</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Mysterious Room Access Door</t>
+          <t>Cửa Vào Căn Phòng Bí Ẩn</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Vào Dark Side</t>
+          <t>Bước vào Bóng Tối</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Enter "The Finale"</t>
+          <t>Vào "The Finale"</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Bàn của Lynae</t>
+          <t>Bàn làm việc của Lynae</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Begin Preparations</t>
+          <t>Bắt đầu Chuẩn Bị</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Rương Kho Báu Khổng Lồ: Giá quá đắt</t>
+          <t>Rương Kho Báu Khổng Lồ: Giá Cả Quá Tay</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Coax Xiaobao</t>
+          <t>Dỗ Dành Tiểu Bảo</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Zhaoyang</t>
+          <t>Triệu Dương</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Baici</t>
+          <t>Bạch Từ</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Gluttonous Chuubill Gulpy</t>
+          <t>Chuubill Gulpy Háu Ăn</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Nhấn "Tắt" lần cuối</t>
+          <t>Nhấn "Tắt" lần cuối nhé.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Blue Feather Butterfly</t>
+          <t>Bướm Lông Xanh</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Bay đến sườn núi</t>
+          <t>Bay lên sườn núi</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Zhiyuan</t>
+          <t>Chí Nguyên</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>: Death Incarnate</t>
+          <t>: Tử Thần Hóa Thân</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Phantom: Crownless</t>
+          <t>Bóng Ma: Crownless</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Kiêu Ngạo</t>
+          <t>Gã đàn ông kiêu căng</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Giấy thông hành sửa chữa Bộ Kỹ Thuật</t>
+          <t>Giấy phép sửa chữa Cục Kỹ thuật</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Abyssal Patricius</t>
+          <t>Quý Tộc Vực Sâu</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Drifting Treasures</t>
+          <t>Kho báu Trôi dạt</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>con chó ốm</t>
+          <t>con chó bệnh tật</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Xem quảng cáo</t>
+          <t>Xem quảng cáo đi</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Mở cổng nhà tù</t>
+          <t>Mở cổng nhà giam</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Excited Fluffguin</t>
+          <t>Chíp chíp! Thích quá!</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Academician</t>
+          <t>Viện Sĩ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Wooden Fence</t>
+          <t>Hàng rào gỗ</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Học sinh gần Khu Arcade</t>
+          <t>Học sinh bên máy trò chơi</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Độ Sâu Giấc Mơ</t>
+          <t>Giấc Mộng Vực Sâu</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Buddy</t>
+          <t>Bạn ơi</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Rogue Assassin</t>
+          <t>Sát Thủ Lang Thang</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Chỉ định Phạm Vi (chỉ kiểm tra khu vực)</t>
+          <t>Phạm Vi Chỉ Định (kiểm tra khu vực)</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Chop Chop</t>
+          <t>Nhanh lên nào</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tắt báo động</t>
+          <t>Tắt báo động đi</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Thời lượng</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Quay lại Shashou Cafe</t>
+          <t>Quay lại Quán Shashou</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Vault Security Door</t>
+          <t>Cửa An Ninh Kho Tàng</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Xinyi</t>
+          <t>Tân Nghi</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Rapper Namipon</t>
+          <t>Namipon Rapper</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Đang chế tác</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Salvage</t>
+          <t>Thu hồi</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Đặt Bảng Gỗ</t>
+          <t>Đặt Wooden Plaque</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Fern Spore</t>
+          <t>Bào tử Dương Xỉ</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Vào Chaos</t>
+          <t>Đi vào Vực Hỗn Mang</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Wutheride Transmitter</t>
+          <t>Máy Truyền Tín Wutheride</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Giải thích lại cho tôi</t>
+          <t>Kể ta nghe thêm một lần nữa đi.</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Reader B</t>
+          <t>Người Đọc B</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Nightmare: Inferno Rider</t>
+          <t>Ác Mộng: Inferno Rider</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu mệt mỏi</t>
+          <t>Nhà Nghiên Cứu Mệt Nhọc</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Hidden Dreams</t>
+          <t>Giấc Mơ Ẩn Giấu</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Học sinh kiêu ngạo</t>
+          <t>Học Sinh Kiêu Ngạo</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Tham gia "Thử thách Giả mạo"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Vào Sonoro Sphere</t>
+          <t>Bước vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Thợ săn</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>- Lưỡi Tham Lam</t>
+          <t>- Lưỡi Dao Tham Lam</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Dungeon_Air Wall Manager_Leave</t>
+          <t>Quản lý Rào Cản Không Gian_Rời</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>: Phantom Pain</t>
+          <t>: Nỗi Đau Ảo Giác</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>KU-Broom</t>
+          <t>KU-Chổi</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Syntony Field</t>
+          <t>Trường Điều Tần</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Carapace: Engine Zero</t>
+          <t>Vỏ Giáp: Động Cơ Số Không</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Học sinh hào hứng</t>
+          <t>Học sinh háo hức</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Điều hướng đến Viện Nghiên cứu</t>
+          <t>Hướng về Viện Nghiên Cứu</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Jinhe</t>
+          <t>Kim Hạ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Tôi muốn giao Sonance Caskets: Septimont</t>
+          <t>Tao muốn giao Cỗ Quan Sonance: Septimont</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Khởi hành</t>
+          <t>Giương buồm ra khơi</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Iceglint Dancer</t>
+          <t>Vũ Công Băng Giá</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Petrified Figure</t>
+          <t>Bức tượng hóa đá</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Rời khỏi phòng bí mật</t>
+          <t>Rời khỏi căn phòng bí mật.</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Thổi tù và</t>
+          <t>Thổi kèn lên</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Zealous Duelist</t>
+          <t>Dũng Sĩ Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Smashed Parts</t>
+          <t>Mảnh vỡ bị đập nát</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Elderly Person</t>
+          <t>Người Già</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Xisha</t>
+          <t>Tây Sa</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Xiaoguan</t>
+          <t>Tiểu Quan</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Những cánh hoa rơi rụng</t>
+          <t>Những cánh hoa rơi lả tả</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Leave Parallel Perception</t>
+          <t>Rời khỏi Cảm Giác Song Song</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Miaoshan</t>
+          <t>Mao Sơn</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Old Lady Vendor</t>
+          <t>Bà Cụ Bán Hàng</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Wuyue</t>
+          <t>Ngũ Nhạc</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Ký ức về Trận chiến khốc liệt</t>
+          <t>Ký Ức Cuộc Chiến Khốc Liệt</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Changfeng</t>
+          <t>Xương Phong</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Mutant Organism: Chirpuff</t>
+          <t>Sinh vật thể đột biến: Chirpuff</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Xukong</t>
+          <t>Hư Không</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Elder Listener</t>
+          <t>Trưởng Lão Lắng Nghe</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Học sinh đang trầm tư</t>
+          <t>Học sinh đang trầm ngâm</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>: "Dream Bonds"</t>
+          <t>: "Giấc Mộng Liên Kết"</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Calcharo Cube</t>
+          <t>Khối Calcharo</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Kangjian</t>
+          <t>Khang Kiện</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>A Secret Shared With Jinhsi</t>
+          <t>Bí Mật Chia Sẻ Cùng Jinhsi</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tắt nhạc</t>
+          <t>Tắt nhạc đi</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Pier</t>
+          <t>Bến tàu</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Phantom: Fae Ignis</t>
+          <t>Bóng Ma: Fae Ignis</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Bia mộ vang vọng giai điệu thiêng</t>
+          <t>Ngôi mộ vang vọng khúc thánh ca</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Thành viên Hiệp hội Tiên phong Nam</t>
+          <t>Thành viên Hiệp hội Tiên phong</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Học sinh nhiệt tình</t>
+          <t>Học Sinh Nhiệt Tình</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Shut Beam Weapon</t>
+          <t>Tắt Vũ Khí Chùm Tia</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Xixi</t>
+          <t>Tây Tây</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Enter Infinite Battle Simulation</t>
+          <t>Bắt đầu Mô Phỏng Chiến Đấu Vô Tận</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Qiulin</t>
+          <t>Thu Lâm</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Chrono Shadow</t>
+          <t>Bóng Thời Gian</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Xem bức tranh tường nhỏ</t>
+          <t>Kiểm tra bức tranh tường nhỏ</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Quan sát sứa</t>
+          <t>Kiểm tra con sứa</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Grand Commander</t>
+          <t>Đại Chỉ Huy</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Vô hiệu hóa camera giám sát</t>
+          <t>Tắt camera giám sát</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Nhân viên nữ thuộc Bộ Phát triển</t>
+          <t>Nhân viên nữ Bộ Phát Triển</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Elevator Switch</t>
+          <t>Công Tắc Thang Máy</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Vào Journeying Paradise</t>
+          <t>Bước vào Thiên Đường Lang Thang</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nhân viên hỗ trợ đã nghỉ việc</t>
+          <t>Nhân Viên Hậu Cần Thất Vọng</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Twisted Obsessions</t>
+          <t>Nỗi Ám Ảnh Quanh Co</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Người phụ nữ ngắm hoa</t>
+          <t>Người Phụ Nữ Ngắm Hoa</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Nghỉ ngơi</t>
+          <t>Nghỉ ngơi đi</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Rời khỏi "Warblade from Above"</t>
+          <t>Rời khỏi "Thanh Kiếm Trời Giáng"</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Creeping Torchpine</t>
+          <t>Thông Đuốc Leo</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Trưởng đội Tuần tra</t>
+          <t>Đội Trưởng Tuần Tra</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Signals Console</t>
+          <t>Bảng điều khiển Tín hiệu</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Tethys Terminal</t>
+          <t>Thiết bị đầu cuối Tethys</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Hướng Dẫn</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Đến Error Cell</t>
+          <t>Đến Khu Vực Lỗi</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tiến vào Deathmatch (Ẩn dụ)</t>
+          <t>Bước vào tử chiến</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Namipon Poster</t>
+          <t>Áp phích Namipon</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Rightless</t>
+          <t>Không có quyền lợi gì hết</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>New Noble Client - Actor 1</t>
+          <t>Khách Hàng Quý Tộc Mới - Diễn Viên 1</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Destroy</t>
+          <t>Hủy Diệt</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Đập máy</t>
+          <t>Tát vào máy</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng khốn khổ</t>
+          <t>Nhân Viên Văn Phòng Khốn Khổ</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Yêu cầu thêm thông tin</t>
+          <t>Hỏi thêm thông tin chi tiết</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Vào Phòng Trưng bày Tro Tàn</t>
+          <t>Bước vào Phòng Trưng Bày Tro Tàn.</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Relay Station Guide</t>
+          <t>Hướng Dẫn Viên Trạm Trung Chuyển</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Rider: Solari Blaze</t>
+          <t>Kỵ Sĩ: Solari Blaze</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Eager Agent</t>
+          <t>Đặc vụ Hăng Hái</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Duelaholic Passenger</t>
+          <t>Hành Khách Nghiện Đối Kháng</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Vào Mặt Tối lần nữa</t>
+          <t>Lại bước vào Bóng Tối</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Sistra</t>
+          <t>Chị ơi</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Pollutant: S</t>
+          <t>Ô nhiễm: S</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Grandma Shirley</t>
+          <t>Bà Shirley</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>(Pat)</t>
+          <t>(Vỗ nhẹ)</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Tree Trunk</t>
+          <t>Thân Cây</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tôi muốn mua đồ</t>
+          <t>Ta muốn mua vài món đồ.</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Wenyu</t>
+          <t>Văn Dư</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Bí ẩn</t>
+          <t>Nhà Nghiên Cứu Bí Ẩn</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>A Young Person's Phantom</t>
+          <t>Ảo Ảnh Của Một Người Trẻ Tuổi</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Chuubill Gulpy</t>
+          <t>Chít-bill Gulpy</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Salvi</t>
+          <t>Cứu...</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Worried Mother</t>
+          <t>Người Mẹ Lo Lắng</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Windler</t>
+          <t>Kẻ Thổi Gió</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Xiang-LEE</t>
+          <t>Hương-LY</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Chuyển thiết kế sàn thành "Carol"</t>
+          <t>Đổi thiết kế sàn thành "Carol"</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Mysterious Cave</t>
+          <t>Hang Động Bí Ẩn</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Phản hồi-recording TARD-E Unit</t>
+          <t>Thiết bị ghi nhận phản hồi TARD-E</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Vàng của Kẻ Ngốc</t>
+          <t>Vàng Giả</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Giáo Đầu Nổ</t>
+          <t>Nhà Nghiên Cứu Thương Nổ</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Ebony Gatekeeper</t>
+          <t>Người Gác Cổng Hắc Ám</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Midnight Ranger</t>
+          <t>Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Play Catchow</t>
+          <t>Chơi Catchow</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Investigate</t>
+          <t>Điều Tra</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>"Lollo Logistics Interal Forum"</t>
+          <t>"Diễn Đàn Nội Bộ Lollo Logistics"</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Huiliu</t>
+          <t>Hồi Lưu</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Uncle Jing</t>
+          <t>Bác Kinh</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Harvest Wonder Bubble</t>
+          <t>Bong bóng Kỳ Diệu Thu hoạch</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Vật liệu trên rương</t>
+          <t>Vật liệu đặt trên rương</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Cô Gái Tinh Nghịch</t>
+          <t>Cô nàng tinh nghịch</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Guanming</t>
+          <t>Quang Minh</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Broken Spacetrek Explorer</t>
+          <t>Tàu Thám Hiểm Không Gian Hỏng</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Hoartoise: Flashy Dance</t>
+          <t>Hoartoise: Vũ Điệu Hoa Lệ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Idle Passerby</t>
+          <t>Người qua đường đứng nhìn</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>About Shiyu</t>
+          <t>Về Shiyu</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Ohm</t>
+          <t>Ohm...</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Đồng Hồ Mặt Trời của Quá Khứ</t>
+          <t>Đồng hồ Mặt Trời của Quá Khứ</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Irritable Outcast</t>
+          <t>Kẻ Bị Ruồng Bỏ Nóng Nảy</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Thử thách Overlord</t>
+          <t>Thử Thách Chúa Tể</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Người Đứng Đầu Fisalia Cuối Cùng Với Nỗi Ám Ảnh</t>
+          <t>Nỗi Ám Ảnh Của Cố Thủ Hiến Fisalia</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Soundless Zone Ambience_Mainstory Exclusive</t>
+          <t>Âm Thanh Vùng Vô Âm - Độc Quyền Cốt Truyện Chính</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tấn công về phía trước</t>
+          <t>Tấn Công về phía trước</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Bulletin Board: City</t>
+          <t>Bảng tin: Thành phố</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Xueji</t>
+          <t>Tuyết Kế</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Shorekeeper Cube</t>
+          <t>Khối Shorekeeper</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Pressure Platform</t>
+          <t>Nền Đỡ Áp Lực</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Công Dân Nói Nhiều</t>
+          <t>Dân Chuyện Trò</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Nightmare: Feilian Beringal</t>
+          <t>Ác Mộng: Feilian Beringal</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Dreamless Dream</t>
+          <t>Giấc Mộng Vô Hồn</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Jie'ming</t>
+          <t>Tiết Minh</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Cowardly Exile</t>
+          <t>Kẻ Lưu Đày Hèn Nhát</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Chengxi</t>
+          <t>Thành Hy</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Status Record</t>
+          <t>Lịch sử Trạng Thái</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Lan Hsin</t>
+          <t>Lan Hsin.</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Đáng Ngờ</t>
+          <t>Nhà Nghiên Cứu Đáng Ngờ</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Bắt đầu Phân Tích</t>
+          <t>Bắt đầu Phân tích</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>KU-Roro Đầu Bếp</t>
+          <t>Jinzhou Station</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>KU-Guard</t>
+          <t>KU-Bảo Vệ</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Ebony Gatekeeper</t>
+          <t>Người Gác Cổng Hắc Ám</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Dòng Nước Trong Thành Phố</t>
+          <t>Waters trong thành phố</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Vào Sonoro Sphere</t>
+          <t>Bước vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Công dân ngạc nhiên</t>
+          <t>Dân làng ngạc nhiên</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Học sinh phân vân</t>
+          <t>Học sinh Đa Tâm</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Gentle Mother</t>
+          <t>Người mẹ dịu dàng</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Thương nhân háo hức</t>
+          <t>Thương Nhân Hăng Hái</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Wilder</t>
+          <t>Kẻ Lang Thang</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Rời Doll Factory</t>
+          <t>Rời Nhà Máy Búp Bê</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nói chuyện với cô gái bên cạnh tấm áp phích</t>
+          <t>Nói chuyện với cô gái đứng cạnh tấm áp phích</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu chóng mặt</t>
+          <t>Nhà Nghiên Cứu Hoa Mắt</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Lightcrest Gladiator</t>
+          <t>Dũng Sĩ Lightcrest</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Dwarf Cassowary</t>
+          <t>Đà Điểu Lùn</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Audio Log 4</t>
+          <t>Nhật Ký Âm Thanh 4</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mức GPA khuyến nghị: 700-1000</t>
+          <t>Mức GPA đề xuất: 700-1000</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Tiến vào "giấc mơ"</t>
+          <t>Bước vào "giấc mơ"</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Exile Resonator</t>
+          <t>Resonator Lưu Đày</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Hairless Kitten</t>
+          <t>Mèo Lông Tím</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Sea Flytrap</t>
+          <t>Cây Bắt Mồi Biển</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad: Impact</t>
+          <t>Lampylumen Myriad: Va chạm.</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Denia: Illusory Descent</t>
+          <t>Denia: Hạ Phàm Ảo Ảnh</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Hoohoo</t>
+          <t>Hú hú</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Xin chào</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>: Dreamborne Malice</t>
+          <t>: Ác Ý Sinh Từ Giấc Mơ</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Lianyue</t>
+          <t>Liên Nguyệt</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Đi lên tầng trên</t>
+          <t>Lên tầng cao hơn</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Insomniac</t>
+          <t>Kẻ mất ngủ</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Black Shores Gardener</t>
+          <t>Người Trồng Trọt Bờ Đen</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Elite Dreadmane: Ice</t>
+          <t>Dreadmane Cấp Tinh Anh: Ice</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Mở giao diện mạng lộ trình</t>
+          <t>Mở giao diện mạng lưới tuyến đường</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Lanternberry</t>
+          <t>Quả Đèn Lồng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Shorekeeper's Illusion</t>
+          <t>Ảo Ảnh Shorekeeper</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Messy Animal Tracks</t>
+          <t>Dấu Vết Thú Rừng Lộn Xộn</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Học sinh bị thương</t>
+          <t>Học Sinh Bị Thương</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Những trang nhật ký bị xé</t>
+          <t>Những Trang Nhật Ký Rách</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Talos: "The Peace Keeper"</t>
+          <t>Talos: "Người Gìn Giữ Hòa Bình"</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Đến Địa điểm Nghỉ ngơi Exostrider</t>
+          <t>Đến Điểm Nghỉ Ngơi của Exostrider</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Photon Barrier Lock</t>
+          <t>Khóa Chắn Photon</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Cậu bé lịch sự</t>
+          <t>Cậu Bé Lễ Độ</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Guan</t>
+          <t>Quan</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Thông báo Board</t>
+          <t>Bảng Thông Báo</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Nhân viên hỗ trợ</t>
+          <t>Đội Ngũ Hỗ Trợ</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Clockwork</t>
+          <t>Cơ khí</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Người phụ nữ rụt rè</t>
+          <t>Người phụ nữ bẽn lẽn</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Mức Glory khuyến nghị: 1-100</t>
+          <t>Cấp Vinh Quang đề xuất: 1-100</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
